--- a/outputs/tables/manuscript/degora_manuscript_tables.xlsx
+++ b/outputs/tables/manuscript/degora_manuscript_tables.xlsx
@@ -728,7 +728,7 @@
         <v>0.26</v>
       </c>
       <c r="J2" t="n">
-        <v>2.26389463830383e-51</v>
+        <v>2.438040379711817e-51</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>0.26</v>
       </c>
       <c r="R2" t="n">
-        <v>2.26389463830383e-51</v>
+        <v>2.438040379711817e-51</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>0.25</v>
       </c>
       <c r="J3" t="n">
-        <v>1.089785108368915e-48</v>
+        <v>1.180600534066325e-48</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>0.24</v>
       </c>
       <c r="R3" t="n">
-        <v>2.533774481512146e-46</v>
+        <v>2.744922354971492e-46</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>0.19</v>
       </c>
       <c r="J4" t="n">
-        <v>7.652962181726839e-36</v>
+        <v>8.241651580321211e-36</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>0.15</v>
       </c>
       <c r="R4" t="n">
-        <v>2.495675735701556e-26</v>
+        <v>2.687650792293985e-26</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>0.28</v>
       </c>
       <c r="J5" t="n">
-        <v>3.43935681240881e-67</v>
+        <v>3.725969880109545e-67</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>0.28</v>
       </c>
       <c r="R5" t="n">
-        <v>3.43935681240881e-67</v>
+        <v>3.725969880109545e-67</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1981,6 +1981,63 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MAIC (Wang 2022, CLI)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>partial (contributor lists)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>yes (local CLI)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>yes (TSV)</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
